--- a/src/fixtures/sample/gstr2b-2025-09.xlsx
+++ b/src/fixtures/sample/gstr2b-2025-09.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,25 +470,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2025/002</v>
+        <v>S01/2025/003</v>
       </c>
       <c r="D6" t="str">
-        <v>20/09/2025</v>
+        <v>17/09/2025</v>
       </c>
       <c r="E6">
-        <v>571120</v>
+        <v>564040</v>
       </c>
       <c r="F6">
-        <v>484000</v>
+        <v>478000</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>43560</v>
+        <v>43020</v>
       </c>
       <c r="I6">
-        <v>43560</v>
+        <v>43020</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>2025-10</v>
       </c>
       <c r="L6" t="str">
-        <v>14/10/2025</v>
+        <v>08/10/2025</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>27AAPFM4821K1ZV</v>
+        <v>29AAKFK3390B1ZB</v>
       </c>
       <c r="B7" t="str">
-        <v>Mahesh Steel Traders</v>
+        <v>Kaveri Packaging</v>
       </c>
       <c r="C7" t="str">
-        <v>S01/2025/003</v>
+        <v>S03/2025/001</v>
       </c>
       <c r="D7" t="str">
-        <v>17/09/2025</v>
+        <v>16/09/2025</v>
       </c>
       <c r="E7">
-        <v>564040</v>
+        <v>142780</v>
       </c>
       <c r="F7">
-        <v>478000</v>
+        <v>121000</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>21780</v>
       </c>
       <c r="H7">
-        <v>43020</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>43020</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2025-10</v>
       </c>
       <c r="L7" t="str">
-        <v>08/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -564,19 +564,19 @@
         <v>Kaveri Packaging</v>
       </c>
       <c r="C8" t="str">
-        <v>S03/2025/001</v>
+        <v>S03/2025/002</v>
       </c>
       <c r="D8" t="str">
-        <v>13/09/2025</v>
+        <v>21/09/2025</v>
       </c>
       <c r="E8">
-        <v>136880</v>
+        <v>126260</v>
       </c>
       <c r="F8">
-        <v>116000</v>
+        <v>107000</v>
       </c>
       <c r="G8">
-        <v>20880</v>
+        <v>19260</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2025-10</v>
       </c>
       <c r="L8" t="str">
-        <v>11/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -605,25 +605,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>29AAKFK3390B1ZB</v>
+        <v>24AAGCA1188M1ZI</v>
       </c>
       <c r="B9" t="str">
-        <v>Kaveri Packaging</v>
+        <v>Anand Polymers</v>
       </c>
       <c r="C9" t="str">
-        <v>S03/2025/002</v>
+        <v>S05/2025/001</v>
       </c>
       <c r="D9" t="str">
         <v>11/09/2025</v>
       </c>
       <c r="E9">
-        <v>148680</v>
+        <v>370520</v>
       </c>
       <c r="F9">
-        <v>126000</v>
+        <v>314000</v>
       </c>
       <c r="G9">
-        <v>22680</v>
+        <v>56520</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2025-10</v>
       </c>
       <c r="L9" t="str">
-        <v>14/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -658,19 +658,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C10" t="str">
-        <v>S05/2025/001</v>
+        <v>S05/2025/002</v>
       </c>
       <c r="D10" t="str">
-        <v>21/09/2025</v>
+        <v>24/09/2025</v>
       </c>
       <c r="E10">
-        <v>376420</v>
+        <v>371700</v>
       </c>
       <c r="F10">
-        <v>319000</v>
+        <v>315000</v>
       </c>
       <c r="G10">
-        <v>57420</v>
+        <v>56700</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -705,19 +705,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C11" t="str">
-        <v>S05/2025/002</v>
+        <v>S05/2025/003</v>
       </c>
       <c r="D11" t="str">
-        <v>21/09/2025</v>
+        <v>14/09/2025</v>
       </c>
       <c r="E11">
-        <v>372880</v>
+        <v>377600</v>
       </c>
       <c r="F11">
-        <v>316000</v>
+        <v>320000</v>
       </c>
       <c r="G11">
-        <v>56880</v>
+        <v>57600</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2025-10</v>
       </c>
       <c r="L11" t="str">
-        <v>13/10/2025</v>
+        <v>11/10/2025</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -746,31 +746,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>24AAGCA1188M1ZI</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B12" t="str">
-        <v>Anand Polymers</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C12" t="str">
-        <v>S05/2025/003</v>
+        <v>SE 1</v>
       </c>
       <c r="D12" t="str">
-        <v>21/09/2025</v>
+        <v>11/09/2025</v>
       </c>
       <c r="E12">
-        <v>376420</v>
+        <v>179360</v>
       </c>
       <c r="F12">
-        <v>319000</v>
+        <v>152000</v>
       </c>
       <c r="G12">
-        <v>57420</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>13680</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>13680</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>2025-10</v>
       </c>
       <c r="L12" t="str">
-        <v>09/10/2025</v>
+        <v>12/10/2025</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -802,22 +802,22 @@
         <v>SE 1</v>
       </c>
       <c r="D13" t="str">
-        <v>15/09/2025</v>
+        <v>24/09/2025</v>
       </c>
       <c r="E13">
-        <v>168740</v>
+        <v>156940</v>
       </c>
       <c r="F13">
-        <v>143000</v>
+        <v>133000</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>12870</v>
+        <v>11970</v>
       </c>
       <c r="I13">
-        <v>12870</v>
+        <v>11970</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2025-10</v>
       </c>
       <c r="L13" t="str">
-        <v>13/10/2025</v>
+        <v>08/10/2025</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B14" t="str">
-        <v>Surya Electricals</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C14" t="str">
-        <v>SE 1</v>
+        <v>S08/2025/001</v>
       </c>
       <c r="D14" t="str">
         <v>11/09/2025</v>
       </c>
       <c r="E14">
-        <v>154580</v>
+        <v>219480</v>
       </c>
       <c r="F14">
-        <v>131000</v>
+        <v>186000</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>33480</v>
       </c>
       <c r="H14">
-        <v>11790</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>11790</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>2025-10</v>
       </c>
       <c r="L14" t="str">
-        <v>10/10/2025</v>
+        <v>14/10/2025</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
@@ -893,19 +893,19 @@
         <v>Ratna Chemicals</v>
       </c>
       <c r="C15" t="str">
-        <v>S08/2025/001</v>
+        <v>S08/2025/002</v>
       </c>
       <c r="D15" t="str">
-        <v>06/09/2025</v>
+        <v>18/09/2025</v>
       </c>
       <c r="E15">
-        <v>201780</v>
+        <v>218300</v>
       </c>
       <c r="F15">
-        <v>171000</v>
+        <v>185000</v>
       </c>
       <c r="G15">
-        <v>30780</v>
+        <v>33300</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>2025-10</v>
       </c>
       <c r="L15" t="str">
-        <v>09/10/2025</v>
+        <v>15/10/2025</v>
       </c>
       <c r="M15" t="str">
         <v>Yes</v>
@@ -934,31 +934,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B16" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C16" t="str">
-        <v>S08/2025/002</v>
+        <v>S09/2025/001</v>
       </c>
       <c r="D16" t="str">
-        <v>26/09/2025</v>
+        <v>20/09/2025</v>
       </c>
       <c r="E16">
-        <v>221840</v>
+        <v>1057280</v>
       </c>
       <c r="F16">
-        <v>188000</v>
+        <v>896000</v>
       </c>
       <c r="G16">
-        <v>33840</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>80640</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>80640</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -967,13 +967,13 @@
         <v>2025-10</v>
       </c>
       <c r="L16" t="str">
-        <v>16/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O16" t="str">
         <v>N</v>
@@ -981,31 +981,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B17" t="str">
-        <v>Metro Motors</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C17" t="str">
-        <v>S09/2025/001</v>
+        <v>S10/2025/001</v>
       </c>
       <c r="D17" t="str">
-        <v>21/09/2025</v>
+        <v>11/09/2025</v>
       </c>
       <c r="E17">
-        <v>1059640</v>
+        <v>312700</v>
       </c>
       <c r="F17">
-        <v>898000</v>
+        <v>265000</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>47700</v>
       </c>
       <c r="H17">
-        <v>80820</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>80820</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1014,13 +1014,13 @@
         <v>2025-10</v>
       </c>
       <c r="L17" t="str">
-        <v>15/10/2025</v>
+        <v>11/10/2025</v>
       </c>
       <c r="M17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N17" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O17" t="str">
         <v>N</v>
@@ -1034,7 +1034,7 @@
         <v>Vindhya Alloys</v>
       </c>
       <c r="C18" t="str">
-        <v>S10/2025/001</v>
+        <v>S10/2025/002</v>
       </c>
       <c r="D18" t="str">
         <v>23/09/2025</v>
@@ -1075,31 +1075,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B19" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C19" t="str">
-        <v>S10/2025/002</v>
+        <v>S12/2025/001</v>
       </c>
       <c r="D19" t="str">
-        <v>05/09/2025</v>
+        <v>16/09/2025</v>
       </c>
       <c r="E19">
-        <v>323320</v>
+        <v>177000</v>
       </c>
       <c r="F19">
-        <v>274000</v>
+        <v>150000</v>
       </c>
       <c r="G19">
-        <v>49320</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>2025-10</v>
       </c>
       <c r="L19" t="str">
-        <v>14/10/2025</v>
+        <v>11/10/2025</v>
       </c>
       <c r="M19" t="str">
         <v>Yes</v>
@@ -1128,25 +1128,25 @@
         <v>Bharat Office Supplies</v>
       </c>
       <c r="C20" t="str">
-        <v>S12/2025/001</v>
+        <v>S12/2025/002</v>
       </c>
       <c r="D20" t="str">
-        <v>02/09/2025</v>
+        <v>14/09/2025</v>
       </c>
       <c r="E20">
-        <v>189980</v>
+        <v>186440</v>
       </c>
       <c r="F20">
-        <v>161000</v>
+        <v>158000</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>14490</v>
+        <v>14220</v>
       </c>
       <c r="I20">
-        <v>14490</v>
+        <v>14220</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>2025-10</v>
       </c>
       <c r="L20" t="str">
-        <v>15/10/2025</v>
+        <v>08/10/2025</v>
       </c>
       <c r="M20" t="str">
         <v>Yes</v>
@@ -1178,22 +1178,22 @@
         <v>S13/2025/001</v>
       </c>
       <c r="D21" t="str">
-        <v>19/09/2025</v>
+        <v>02/09/2025</v>
       </c>
       <c r="E21">
-        <v>97940</v>
+        <v>84960</v>
       </c>
       <c r="F21">
-        <v>83000</v>
+        <v>72000</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>7470</v>
+        <v>6480</v>
       </c>
       <c r="I21">
-        <v>7470</v>
+        <v>6480</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2025-10</v>
       </c>
       <c r="L21" t="str">
-        <v>09/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1225,7 +1225,7 @@
         <v>S14/2025/001</v>
       </c>
       <c r="D22" t="str">
-        <v>10/09/2025</v>
+        <v>24/09/2025</v>
       </c>
       <c r="E22">
         <v>139240</v>
@@ -1272,16 +1272,16 @@
         <v>S15/2025/001</v>
       </c>
       <c r="D23" t="str">
-        <v>06/09/2025</v>
+        <v>12/09/2025</v>
       </c>
       <c r="E23">
-        <v>40120</v>
+        <v>47200</v>
       </c>
       <c r="F23">
-        <v>34000</v>
+        <v>40000</v>
       </c>
       <c r="G23">
-        <v>6120</v>
+        <v>7200</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2025-10</v>
       </c>
       <c r="L23" t="str">
-        <v>08/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1319,16 +1319,16 @@
         <v>S15/2025/002</v>
       </c>
       <c r="D24" t="str">
-        <v>12/09/2025</v>
+        <v>11/09/2025</v>
       </c>
       <c r="E24">
-        <v>56640</v>
+        <v>38940</v>
       </c>
       <c r="F24">
-        <v>48000</v>
+        <v>33000</v>
       </c>
       <c r="G24">
-        <v>8640</v>
+        <v>5940</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2025-10</v>
       </c>
       <c r="L24" t="str">
-        <v>09/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1366,16 +1366,16 @@
         <v>S15/2025/003</v>
       </c>
       <c r="D25" t="str">
-        <v>14/09/2025</v>
+        <v>21/09/2025</v>
       </c>
       <c r="E25">
-        <v>55460</v>
+        <v>31860</v>
       </c>
       <c r="F25">
-        <v>47000</v>
+        <v>27000</v>
       </c>
       <c r="G25">
-        <v>8460</v>
+        <v>4860</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2025-10</v>
       </c>
       <c r="L25" t="str">
-        <v>13/10/2025</v>
+        <v>14/10/2025</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1413,16 +1413,16 @@
         <v>S16/2025/001</v>
       </c>
       <c r="D26" t="str">
-        <v>07/09/2025</v>
+        <v>12/09/2025</v>
       </c>
       <c r="E26">
-        <v>84960</v>
+        <v>71980</v>
       </c>
       <c r="F26">
-        <v>72000</v>
+        <v>61000</v>
       </c>
       <c r="G26">
-        <v>12960</v>
+        <v>10980</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>2025-10</v>
       </c>
       <c r="L26" t="str">
-        <v>14/10/2025</v>
+        <v>13/10/2025</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
@@ -1460,16 +1460,16 @@
         <v>S16/2025/002</v>
       </c>
       <c r="D27" t="str">
-        <v>19/09/2025</v>
+        <v>08/09/2025</v>
       </c>
       <c r="E27">
-        <v>73160</v>
+        <v>67260</v>
       </c>
       <c r="F27">
-        <v>62000</v>
+        <v>57000</v>
       </c>
       <c r="G27">
-        <v>11160</v>
+        <v>10260</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>2025-10</v>
       </c>
       <c r="L27" t="str">
-        <v>12/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1507,7 +1507,7 @@
         <v>S17/2025/001</v>
       </c>
       <c r="D28" t="str">
-        <v>21/09/2025</v>
+        <v>14/09/2025</v>
       </c>
       <c r="E28">
         <v>56640</v>
@@ -1531,7 +1531,7 @@
         <v>2025-10</v>
       </c>
       <c r="L28" t="str">
-        <v>14/10/2025</v>
+        <v>09/10/2025</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1551,25 +1551,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C29" t="str">
-        <v>S18/2025/001</v>
+        <v>S18/2025/002</v>
       </c>
       <c r="D29" t="str">
-        <v>16/09/2025</v>
+        <v>25/09/2025</v>
       </c>
       <c r="E29">
-        <v>171100</v>
+        <v>164020</v>
       </c>
       <c r="F29">
-        <v>145000</v>
+        <v>139000</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>13050</v>
+        <v>12510</v>
       </c>
       <c r="I29">
-        <v>13050</v>
+        <v>12510</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2025-10</v>
       </c>
       <c r="L29" t="str">
-        <v>08/10/2025</v>
+        <v>09/10/2025</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1598,25 +1598,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C30" t="str">
-        <v>S18/2025/002</v>
+        <v>S18/2025/003</v>
       </c>
       <c r="D30" t="str">
-        <v>15/09/2025</v>
+        <v>12/09/2025</v>
       </c>
       <c r="E30">
-        <v>156940</v>
+        <v>164020</v>
       </c>
       <c r="F30">
-        <v>133000</v>
+        <v>139000</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>11970</v>
+        <v>12510</v>
       </c>
       <c r="I30">
-        <v>11970</v>
+        <v>12510</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2025-10</v>
       </c>
       <c r="L30" t="str">
-        <v>15/10/2025</v>
+        <v>14/10/2025</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
@@ -1639,31 +1639,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B31" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C31" t="str">
-        <v>S18/2025/003</v>
+        <v>S19/2025/001</v>
       </c>
       <c r="D31" t="str">
         <v>16/09/2025</v>
       </c>
       <c r="E31">
-        <v>164020</v>
+        <v>96760</v>
       </c>
       <c r="F31">
-        <v>139000</v>
+        <v>82000</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="H31">
-        <v>12510</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>12510</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>2025-10</v>
       </c>
       <c r="L31" t="str">
-        <v>13/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M31" t="str">
         <v>Yes</v>
@@ -1692,19 +1692,19 @@
         <v>Sundar Printing Works</v>
       </c>
       <c r="C32" t="str">
-        <v>S19/2025/001</v>
+        <v>S19/2025/002</v>
       </c>
       <c r="D32" t="str">
         <v>03/09/2025</v>
       </c>
       <c r="E32">
-        <v>96760</v>
+        <v>107380</v>
       </c>
       <c r="F32">
-        <v>82000</v>
+        <v>91000</v>
       </c>
       <c r="G32">
-        <v>14760</v>
+        <v>16380</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>2025-10</v>
       </c>
       <c r="L32" t="str">
-        <v>11/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
@@ -1733,31 +1733,31 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B33" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C33" t="str">
-        <v>S19/2025/002</v>
+        <v>S20/2025/001</v>
       </c>
       <c r="D33" t="str">
-        <v>19/09/2025</v>
+        <v>24/09/2025</v>
       </c>
       <c r="E33">
-        <v>100300</v>
+        <v>133340</v>
       </c>
       <c r="F33">
-        <v>85000</v>
+        <v>113000</v>
       </c>
       <c r="G33">
-        <v>15300</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>10170</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>10170</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>2025-10</v>
       </c>
       <c r="L33" t="str">
-        <v>10/10/2025</v>
+        <v>12/10/2025</v>
       </c>
       <c r="M33" t="str">
         <v>Yes</v>
@@ -1786,25 +1786,25 @@
         <v>Ashoka Civil Works</v>
       </c>
       <c r="C34" t="str">
-        <v>S20/2025/001</v>
+        <v>S20/2025/002</v>
       </c>
       <c r="D34" t="str">
-        <v>25/09/2025</v>
+        <v>26/09/2025</v>
       </c>
       <c r="E34">
-        <v>154580</v>
+        <v>147500</v>
       </c>
       <c r="F34">
-        <v>131000</v>
+        <v>125000</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>11790</v>
+        <v>11250</v>
       </c>
       <c r="I34">
-        <v>11790</v>
+        <v>11250</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>2025-10</v>
       </c>
       <c r="L34" t="str">
-        <v>15/10/2025</v>
+        <v>11/10/2025</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
@@ -1827,31 +1827,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B35" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C35" t="str">
-        <v>S20/2025/002</v>
+        <v>S21/2025/001</v>
       </c>
       <c r="D35" t="str">
-        <v>09/09/2025</v>
+        <v>14/09/2025</v>
       </c>
       <c r="E35">
-        <v>140420</v>
+        <v>188800</v>
       </c>
       <c r="F35">
-        <v>119000</v>
+        <v>160000</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="H35">
-        <v>10710</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>10710</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2025-10</v>
       </c>
       <c r="L35" t="str">
-        <v>12/10/2025</v>
+        <v>13/10/2025</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1880,19 +1880,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C36" t="str">
-        <v>S21/2025/001</v>
+        <v>S21/2025/003</v>
       </c>
       <c r="D36" t="str">
-        <v>14/09/2025</v>
+        <v>25/09/2025</v>
       </c>
       <c r="E36">
-        <v>189980</v>
+        <v>204140</v>
       </c>
       <c r="F36">
-        <v>161000</v>
+        <v>173000</v>
       </c>
       <c r="G36">
-        <v>28980</v>
+        <v>31140</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2025-10</v>
       </c>
       <c r="L36" t="str">
-        <v>11/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1921,31 +1921,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAGFM1167A1ZO</v>
       </c>
       <c r="B37" t="str">
-        <v>Nova Instruments</v>
+        <v>Meridian Housekeeping</v>
       </c>
       <c r="C37" t="str">
-        <v>S21/2025/002</v>
+        <v>S22/2025/001</v>
       </c>
       <c r="D37" t="str">
         <v>09/09/2025</v>
       </c>
       <c r="E37">
-        <v>199420</v>
+        <v>206500</v>
       </c>
       <c r="F37">
-        <v>169000</v>
+        <v>175000</v>
       </c>
       <c r="G37">
-        <v>30420</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>15750</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>15750</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2025-10</v>
       </c>
       <c r="L37" t="str">
-        <v>14/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1968,25 +1968,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>09AAJFY5523C1Z3</v>
       </c>
       <c r="B38" t="str">
-        <v>Nova Instruments</v>
+        <v>Yamuna Agro Products</v>
       </c>
       <c r="C38" t="str">
-        <v>S21/2025/003</v>
+        <v>S24/2025/001</v>
       </c>
       <c r="D38" t="str">
-        <v>20/09/2025</v>
+        <v>13/09/2025</v>
       </c>
       <c r="E38">
-        <v>182900</v>
+        <v>162840</v>
       </c>
       <c r="F38">
-        <v>155000</v>
+        <v>138000</v>
       </c>
       <c r="G38">
-        <v>27900</v>
+        <v>24840</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2025-10</v>
       </c>
       <c r="L38" t="str">
-        <v>10/10/2025</v>
+        <v>13/10/2025</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2015,31 +2015,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>27AAGFM1167A1ZO</v>
+        <v>09AAJFY5523C1Z3</v>
       </c>
       <c r="B39" t="str">
-        <v>Meridian Housekeeping</v>
+        <v>Yamuna Agro Products</v>
       </c>
       <c r="C39" t="str">
-        <v>S22/2025/001</v>
+        <v>S24/2025/002</v>
       </c>
       <c r="D39" t="str">
-        <v>03/09/2025</v>
+        <v>08/09/2025</v>
       </c>
       <c r="E39">
-        <v>202960</v>
+        <v>166380</v>
       </c>
       <c r="F39">
-        <v>172000</v>
+        <v>141000</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>25380</v>
       </c>
       <c r="H39">
-        <v>15480</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>15480</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2025-10</v>
       </c>
       <c r="L39" t="str">
-        <v>09/10/2025</v>
+        <v>10/10/2025</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2068,10 +2068,10 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C40" t="str">
-        <v>S24/2025/001</v>
+        <v>S24/2025/003</v>
       </c>
       <c r="D40" t="str">
-        <v>10/09/2025</v>
+        <v>07/09/2025</v>
       </c>
       <c r="E40">
         <v>158120</v>
@@ -2095,7 +2095,7 @@
         <v>2025-10</v>
       </c>
       <c r="L40" t="str">
-        <v>16/10/2025</v>
+        <v>15/10/2025</v>
       </c>
       <c r="M40" t="str">
         <v>Yes</v>
@@ -2109,31 +2109,31 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>27AABCZ9934D1Z1</v>
       </c>
       <c r="B41" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Zenith Tooling</v>
       </c>
       <c r="C41" t="str">
-        <v>S24/2025/002</v>
+        <v>S25/2025/001</v>
       </c>
       <c r="D41" t="str">
-        <v>19/09/2025</v>
+        <v>17/09/2025</v>
       </c>
       <c r="E41">
-        <v>156940</v>
+        <v>35400</v>
       </c>
       <c r="F41">
-        <v>133000</v>
+        <v>30000</v>
       </c>
       <c r="G41">
-        <v>23940</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2025-10</v>
       </c>
       <c r="L41" t="str">
-        <v>13/10/2025</v>
+        <v>12/10/2025</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2151,106 +2151,12 @@
         <v/>
       </c>
       <c r="O41" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>09AAJFY5523C1Z3</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Yamuna Agro Products</v>
-      </c>
-      <c r="C42" t="str">
-        <v>S24/2025/003</v>
-      </c>
-      <c r="D42" t="str">
-        <v>17/09/2025</v>
-      </c>
-      <c r="E42">
-        <v>160480</v>
-      </c>
-      <c r="F42">
-        <v>136000</v>
-      </c>
-      <c r="G42">
-        <v>24480</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="L42" t="str">
-        <v>08/10/2025</v>
-      </c>
-      <c r="M42" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>27AABCZ9934D1Z1</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Zenith Tooling</v>
-      </c>
-      <c r="C43" t="str">
-        <v>S25/2025/001</v>
-      </c>
-      <c r="D43" t="str">
-        <v>16/09/2025</v>
-      </c>
-      <c r="E43">
-        <v>46020</v>
-      </c>
-      <c r="F43">
-        <v>39000</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>3510</v>
-      </c>
-      <c r="I43">
-        <v>3510</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="L43" t="str">
-        <v>08/10/2025</v>
-      </c>
-      <c r="M43" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O41"/>
   </ignoredErrors>
 </worksheet>
 </file>
